--- a/artfynd/S 4104-2023 artfynd.xlsx
+++ b/artfynd/S 4104-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AZ34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123701329</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -909,6 +919,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123316757</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1025,6 +1040,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123316780</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1141,6 +1161,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123316788</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1263,6 +1288,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123701345</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1370,6 +1400,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123701737</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1487,6 +1522,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123316748</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1609,6 +1649,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123701658</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1716,6 +1761,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123701689</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1823,6 +1873,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123701719</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1940,6 +1995,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123316761</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2057,6 +2117,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123316775</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2174,6 +2239,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123316801</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2290,6 +2360,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123316797</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2405,6 +2480,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83572584</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2520,6 +2600,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83572585</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2635,6 +2720,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83572607</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2750,6 +2840,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83572613</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2865,6 +2960,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83572616</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2980,6 +3080,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83572639</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3095,6 +3200,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83572644</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3210,6 +3320,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83572687</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3325,6 +3440,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83572708</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3440,6 +3560,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83572711</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3555,6 +3680,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83572727</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3670,6 +3800,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83572730</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3785,6 +3920,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83572736</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3900,6 +4040,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83572770</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4015,6 +4160,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83572818</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4130,6 +4280,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83572826</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4243,6 +4398,11 @@
       <c r="AY32" t="inlineStr">
         <is>
           <t>Trädportalen</t>
+        </is>
+      </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83572840</t>
         </is>
       </c>
     </row>
@@ -4361,6 +4521,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123316751</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4467,8 +4632,48 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123701745</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>